--- a/frontend/public/webtest/Testing_Template_11152022.xlsx
+++ b/frontend/public/webtest/Testing_Template_11152022.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -875,555 +875,567 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Difference between FDA and CDER-CBER version</v>
+        <v>6)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Labeling Section [simple] "false positive" within Drug/Laboratory Test Interactions | within Non-PLR Format (CDER-CBER version)</v>
+      </c>
+      <c r="C37" t="str">
+        <v xml:space="preserve">FDA   </v>
+      </c>
+      <c r="D37" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/87771</v>
+      </c>
+      <c r="E37" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/87771</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1,310</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>6)</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Labeling Section [simple] "false positive" within Drug/Laboratory Test Interactions | within Non-PLR Format (CDER-CBER version)</v>
-      </c>
       <c r="C38" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>CDER-CBER</v>
       </c>
       <c r="D38" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/87771</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/search/spl-summaries/criteria/87770</v>
       </c>
       <c r="E38" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/87771</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/87770</v>
       </c>
       <c r="F38" t="str">
-        <v>1,310</v>
+        <v>1,260</v>
       </c>
     </row>
     <row r="39">
       <c r="C39" t="str">
-        <v>CDER-CBER</v>
-      </c>
-      <c r="D39" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/search/spl-summaries/criteria/87770</v>
+        <v>FDA (test)</v>
       </c>
       <c r="E39" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/87770</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/341</v>
       </c>
       <c r="F39" t="str">
-        <v>1,260</v>
+        <v>1,315</v>
       </c>
     </row>
     <row r="40">
       <c r="C40" t="str">
-        <v>FDA (test)</v>
+        <v>CDER-CBER (test)</v>
       </c>
       <c r="E40" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/341</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/351</v>
       </c>
       <c r="F40" t="str">
-        <v>1,315</v>
+        <v>1,273</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="str">
-        <v>CDER-CBER (test)</v>
+        <v>FDA (dev)</v>
       </c>
       <c r="E41" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/351</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2326</v>
       </c>
       <c r="F41" t="str">
-        <v>1,273</v>
+        <v>1,315</v>
       </c>
     </row>
     <row r="42">
       <c r="C42" t="str">
-        <v>FDA (dev)</v>
+        <v>CDER-CBER (dev)</v>
       </c>
       <c r="E42" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2326</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2315</v>
       </c>
       <c r="F42" t="str">
-        <v>1,315</v>
+        <v>1,273</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" t="str">
-        <v>CDER-CBER (dev)</v>
+        <v>Public</v>
       </c>
       <c r="E43" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2315</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215093</v>
       </c>
       <c r="F43" t="str">
-        <v>1,273</v>
+        <v>1,310</v>
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="str">
+        <v>7)</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Labeling Section [simple] "diabetes" within Indications and Usage; RLD | within PLR format (CDER-CBER version)</v>
+      </c>
       <c r="C44" t="str">
-        <v>Public</v>
+        <v xml:space="preserve">FDA   </v>
+      </c>
+      <c r="D44" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/87849</v>
       </c>
       <c r="E44" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215093</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/87849</v>
       </c>
       <c r="F44" t="str">
-        <v>1,310</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>7)</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Labeling Section [simple] "diabetes" within Indications and Usage; RLD | within PLR format (CDER-CBER version)</v>
-      </c>
       <c r="C45" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>CDER-CBER</v>
       </c>
       <c r="D45" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/87849</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/search/spl-summaries/criteria/87851</v>
       </c>
       <c r="E45" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/87849</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/87851</v>
       </c>
       <c r="F45" t="str">
-        <v>171</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" t="str">
-        <v>CDER-CBER</v>
-      </c>
-      <c r="D46" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/search/spl-summaries/criteria/87851</v>
+        <v>FDA (test)</v>
       </c>
       <c r="E46" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/87851</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/343</v>
       </c>
       <c r="F46" t="str">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47">
       <c r="C47" t="str">
-        <v>FDA (test)</v>
+        <v>CDER-CBER (test)</v>
       </c>
       <c r="E47" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/343</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/540</v>
       </c>
       <c r="F47" t="str">
-        <v>169</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48">
       <c r="C48" t="str">
-        <v>CDER-CBER (test)</v>
+        <v>FDA (dev)</v>
       </c>
       <c r="E48" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/540</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2329</v>
       </c>
       <c r="F48" t="str">
-        <v>137</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49">
       <c r="C49" t="str">
-        <v>FDA (dev)</v>
+        <v>CDER-CBER (dev)</v>
       </c>
       <c r="E49" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2329</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2316</v>
       </c>
       <c r="F49" t="str">
-        <v>169</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50">
       <c r="C50" t="str">
-        <v>CDER-CBER (dev)</v>
+        <v>Public</v>
       </c>
       <c r="E50" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2316</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215839</v>
       </c>
       <c r="F50" t="str">
-        <v>137</v>
+        <v>4,254</v>
+      </c>
+      <c r="G50" t="str">
+        <v>**No RLD</v>
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="str">
+        <v>8)</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Chemical Structure (1)Naphthalene [substructure] with NDA</v>
+      </c>
       <c r="C51" t="str">
-        <v>Public</v>
+        <v xml:space="preserve">FDA   </v>
+      </c>
+      <c r="D51" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117460</v>
       </c>
       <c r="E51" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215839</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117460</v>
       </c>
       <c r="F51" t="str">
-        <v>4,254</v>
+        <v>97</v>
       </c>
       <c r="G51" t="str">
-        <v>**No RLD</v>
+        <v>error with query- CDER-CBER platform</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
-        <v>FDA version only</v>
+      <c r="C52" t="str">
+        <v>FDA (test)</v>
+      </c>
+      <c r="D52" t="str">
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/344</v>
+      </c>
+      <c r="E52" t="str">
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/344</v>
+      </c>
+      <c r="F52" t="str">
+        <v>108</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <v>8)</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Chemical Structure (1)Naphthalene [substructure] with NDA</v>
-      </c>
       <c r="C53" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>FDA (dev)</v>
       </c>
       <c r="D53" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117460</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/2331</v>
       </c>
       <c r="E53" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117460</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2331</v>
       </c>
       <c r="F53" t="str">
-        <v>97</v>
-      </c>
-      <c r="G53" t="str">
-        <v>error with query- CDER-CBER platform</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54">
       <c r="C54" t="str">
-        <v>FDA (test)</v>
+        <v>Public</v>
       </c>
       <c r="D54" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/344</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/215729</v>
       </c>
       <c r="E54" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/344</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215729</v>
       </c>
       <c r="F54" t="str">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="str">
+        <v>9)</v>
+      </c>
+      <c r="B55" t="str">
+        <v xml:space="preserve">MedDRA acute liver failure </v>
+      </c>
       <c r="C55" t="str">
-        <v>FDA (dev)</v>
+        <v xml:space="preserve">FDA   </v>
       </c>
       <c r="D55" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/2331</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/87772</v>
       </c>
       <c r="E55" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2331</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/87772</v>
       </c>
       <c r="F55" t="str">
-        <v>108</v>
+        <v>1,135</v>
       </c>
     </row>
     <row r="56">
       <c r="C56" t="str">
-        <v>Public</v>
-      </c>
-      <c r="D56" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/215729</v>
+        <v>FDA (test)</v>
       </c>
       <c r="E56" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215729</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/345</v>
       </c>
       <c r="F56" t="str">
-        <v>106</v>
+        <v>1,133</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v>9)</v>
-      </c>
-      <c r="B57" t="str">
-        <v xml:space="preserve">MedDRA acute liver failure </v>
-      </c>
       <c r="C57" t="str">
-        <v xml:space="preserve">FDA   </v>
-      </c>
-      <c r="D57" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/87772</v>
+        <v>FDA (dev)</v>
       </c>
       <c r="E57" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/87772</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2330</v>
       </c>
       <c r="F57" t="str">
-        <v>1,135</v>
+        <v>1,138</v>
       </c>
     </row>
     <row r="58">
       <c r="C58" t="str">
-        <v>FDA (test)</v>
+        <v>Public</v>
       </c>
       <c r="E58" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/345</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215097</v>
       </c>
       <c r="F58" t="str">
-        <v>1,133</v>
+        <v>1,127</v>
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="str">
+        <v>10)</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Chemical Structure (2)Dibenzene [substructure] with NDA</v>
+      </c>
       <c r="C59" t="str">
-        <v>FDA (dev)</v>
+        <v xml:space="preserve">FDA   </v>
+      </c>
+      <c r="D59" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/88969</v>
       </c>
       <c r="E59" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2330</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/88969</v>
       </c>
       <c r="F59" t="str">
-        <v>1,138</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60">
       <c r="C60" t="str">
-        <v>Public</v>
+        <v>FDA (test)</v>
+      </c>
+      <c r="D60" t="str">
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1197</v>
       </c>
       <c r="E60" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/215097</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1197</v>
       </c>
       <c r="F60" t="str">
-        <v>1,127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
-        <v>10)</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Chemical Structure (2)Dibenzene [substructure] with NDA</v>
-      </c>
       <c r="C61" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>FDA (dev)</v>
       </c>
       <c r="D61" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/88969</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/2492</v>
       </c>
       <c r="E61" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/88969</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2492</v>
       </c>
       <c r="F61" t="str">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62">
       <c r="C62" t="str">
-        <v>FDA (test)</v>
+        <v>Public</v>
       </c>
       <c r="D62" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1197</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/229025</v>
       </c>
       <c r="E62" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1197</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/229025</v>
       </c>
       <c r="F62" t="str">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="str">
+        <v>11)</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Labeling Section [advanced] "Pregnancy " In 8.1 pregnancy (PLR or non-PLR)</v>
+      </c>
       <c r="C63" t="str">
-        <v>FDA (dev)</v>
-      </c>
-      <c r="D63" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/2492</v>
+        <v xml:space="preserve">FDA   </v>
       </c>
       <c r="E63" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2492</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/89031</v>
       </c>
       <c r="F63" t="str">
-        <v>105</v>
+        <v>31,204</v>
       </c>
     </row>
     <row r="64">
       <c r="C64" t="str">
-        <v>Public</v>
-      </c>
-      <c r="D64" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/229025</v>
+        <v>CDER-CBER</v>
       </c>
       <c r="E64" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/229025</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/89023</v>
       </c>
       <c r="F64" t="str">
-        <v>105</v>
+        <v>16,914</v>
+      </c>
+      <c r="G64" t="str">
+        <v>PLR</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v>11)</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Labeling Section [advanced] "Pregnancy " In 8.1 pregnancy (PLR or non-PLR)</v>
-      </c>
       <c r="C65" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>CDER-CBER</v>
       </c>
       <c r="E65" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/89031</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/89024</v>
       </c>
       <c r="F65" t="str">
-        <v>31,204</v>
+        <v>14,590</v>
+      </c>
+      <c r="G65" t="str">
+        <v>non-PLR</v>
       </c>
     </row>
     <row r="66">
       <c r="C66" t="str">
-        <v>CDER-CBER</v>
+        <v>FDA (test)</v>
       </c>
       <c r="E66" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/89023</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/541</v>
       </c>
       <c r="F66" t="str">
-        <v>16,914</v>
-      </c>
-      <c r="G66" t="str">
-        <v>PLR</v>
+        <v>31,209</v>
       </c>
     </row>
     <row r="67">
       <c r="C67" t="str">
-        <v>CDER-CBER</v>
+        <v>CDER-CBER (test)</v>
       </c>
       <c r="E67" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/89024</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/542</v>
       </c>
       <c r="F67" t="str">
-        <v>14,590</v>
+        <v>16,919</v>
       </c>
       <c r="G67" t="str">
-        <v>non-PLR</v>
+        <v>PLR</v>
       </c>
     </row>
     <row r="68">
       <c r="C68" t="str">
-        <v>FDA (test)</v>
+        <v>CDER-CBER (test)</v>
       </c>
       <c r="E68" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/541</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/543</v>
       </c>
       <c r="F68" t="str">
-        <v>31,209</v>
+        <v>14,590</v>
+      </c>
+      <c r="G68" t="str">
+        <v>non-PLR</v>
       </c>
     </row>
     <row r="69">
       <c r="C69" t="str">
-        <v>CDER-CBER (test)</v>
+        <v>FDA (dev)</v>
       </c>
       <c r="E69" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/542</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2501</v>
       </c>
       <c r="F69" t="str">
-        <v>16,919</v>
-      </c>
-      <c r="G69" t="str">
-        <v>PLR</v>
+        <v>31,209</v>
       </c>
     </row>
     <row r="70">
       <c r="C70" t="str">
-        <v>CDER-CBER (test)</v>
+        <v>CDER-CBER (dev)</v>
       </c>
       <c r="E70" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/543</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2502</v>
       </c>
       <c r="F70" t="str">
-        <v>14,590</v>
+        <v>16,919</v>
       </c>
       <c r="G70" t="str">
-        <v>non-PLR</v>
+        <v>PLR</v>
       </c>
     </row>
     <row r="71">
       <c r="C71" t="str">
-        <v>FDA (dev)</v>
+        <v>CDER-CBER (dev)</v>
       </c>
       <c r="E71" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2501</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2503</v>
       </c>
       <c r="F71" t="str">
-        <v>31,209</v>
+        <v>14,590</v>
+      </c>
+      <c r="G71" t="str">
+        <v>non-PLR</v>
       </c>
     </row>
     <row r="72">
       <c r="C72" t="str">
-        <v>CDER-CBER (dev)</v>
+        <v>Public</v>
       </c>
       <c r="E72" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2502</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/229507</v>
       </c>
       <c r="F72" t="str">
-        <v>16,919</v>
-      </c>
-      <c r="G72" t="str">
-        <v>PLR</v>
+        <v>31,089</v>
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="str">
+        <v>12)</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ROA (Oral) and ANDA</v>
+      </c>
       <c r="C73" t="str">
-        <v>CDER-CBER (dev)</v>
+        <v xml:space="preserve">FDA   </v>
+      </c>
+      <c r="D73" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117447</v>
       </c>
       <c r="E73" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2503</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117447</v>
       </c>
       <c r="F73" t="str">
-        <v>14,590</v>
+        <v>28,671</v>
       </c>
       <c r="G73" t="str">
-        <v>non-PLR</v>
+        <v>waiting for production, fake url; updated with correct production URL Sept. 2022</v>
       </c>
     </row>
     <row r="74">
       <c r="C74" t="str">
-        <v>Public</v>
+        <v>CDER-CBER</v>
+      </c>
+      <c r="D74" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/search/spl-summaries/criteria/117448</v>
       </c>
       <c r="E74" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/229507</v>
+        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/117448</v>
       </c>
       <c r="F74" t="str">
-        <v>31,089</v>
+        <v>28,674</v>
+      </c>
+      <c r="G74" t="str">
+        <v>waiting for production, fake url; updated with correct production URL Sept. 2022</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v>12)</v>
-      </c>
-      <c r="B75" t="str">
-        <v>ROA (Oral) and ANDA</v>
-      </c>
       <c r="C75" t="str">
-        <v xml:space="preserve">FDA   </v>
-      </c>
-      <c r="D75" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117447</v>
+        <v>FDA (test)</v>
       </c>
       <c r="E75" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117447</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/538</v>
       </c>
       <c r="F75" t="str">
-        <v>28,671</v>
-      </c>
-      <c r="G75" t="str">
-        <v>waiting for production, fake url; updated with correct production URL Sept. 2022</v>
+        <v>26,760</v>
       </c>
     </row>
     <row r="76">
       <c r="C76" t="str">
-        <v>CDER-CBER</v>
-      </c>
-      <c r="D76" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/search/spl-summaries/criteria/117448</v>
+        <v>CDER-CBER (test)</v>
       </c>
       <c r="E76" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel-r/ui/spl-summaries/criteria/117448</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/540</v>
       </c>
       <c r="F76" t="str">
-        <v>28,674</v>
-      </c>
-      <c r="G76" t="str">
-        <v>waiting for production, fake url; updated with correct production URL Sept. 2022</v>
+        <v>26,763</v>
       </c>
     </row>
     <row r="77">
       <c r="C77" t="str">
-        <v>FDA (test)</v>
+        <v>FDA (dev)</v>
       </c>
       <c r="E77" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/538</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2499</v>
       </c>
       <c r="F77" t="str">
         <v>26,760</v>
@@ -1431,52 +1443,64 @@
     </row>
     <row r="78">
       <c r="C78" t="str">
-        <v>CDER-CBER (test)</v>
+        <v>CDER-CBER (dev)</v>
       </c>
       <c r="E78" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel-r/ui/spl-summaries/criteria/540</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2500</v>
       </c>
       <c r="F78" t="str">
         <v>26,763</v>
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="str">
+        <v>13)</v>
+      </c>
+      <c r="B79" t="str">
+        <v>MedDRA Terms "acute liver failure" or PT or LLTs within WARNINGS AND PRECAUTIONS</v>
+      </c>
       <c r="C79" t="str">
-        <v>FDA (dev)</v>
+        <v xml:space="preserve">FDA   </v>
+      </c>
+      <c r="D79" t="str">
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117445</v>
       </c>
       <c r="E79" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/2499</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117445</v>
       </c>
       <c r="F79" t="str">
-        <v>26,760</v>
+        <v>565</v>
+      </c>
+      <c r="G79" t="str">
+        <v>added Sept 2022</v>
       </c>
     </row>
     <row r="80">
       <c r="C80" t="str">
-        <v>CDER-CBER (dev)</v>
+        <v>FDA (test)</v>
+      </c>
+      <c r="D80" t="str">
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1191</v>
       </c>
       <c r="E80" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel-r/ui/spl-summaries/criteria/2500</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1191</v>
       </c>
       <c r="F80" t="str">
-        <v>26,763</v>
+        <v>565</v>
+      </c>
+      <c r="G80" t="str">
+        <v>added Sept 2022</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>13)</v>
-      </c>
-      <c r="B81" t="str">
-        <v>MedDRA Terms "acute liver failure" or PT or LLTs within WARNINGS AND PRECAUTIONS</v>
-      </c>
       <c r="C81" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>FDA (dev)</v>
       </c>
       <c r="D81" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117445</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3037</v>
       </c>
       <c r="E81" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117445</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3037</v>
       </c>
       <c r="F81" t="str">
         <v>565</v>
@@ -1486,17 +1510,23 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="str">
+        <v>14)</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Labeling Section(s) [simple] "screen for" within HIGHLIGHTS</v>
+      </c>
       <c r="C82" t="str">
-        <v>FDA (test)</v>
+        <v xml:space="preserve">FDA   </v>
       </c>
       <c r="D82" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1191</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117446</v>
       </c>
       <c r="E82" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1191</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117446</v>
       </c>
       <c r="F82" t="str">
-        <v>565</v>
+        <v>1,257</v>
       </c>
       <c r="G82" t="str">
         <v>added Sept 2022</v>
@@ -1504,42 +1534,59 @@
     </row>
     <row r="83">
       <c r="C83" t="str">
-        <v>FDA (dev)</v>
+        <v>FDA (test)</v>
       </c>
       <c r="D83" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3037</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1192</v>
       </c>
       <c r="E83" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3037</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1192</v>
       </c>
       <c r="F83" t="str">
-        <v>565</v>
+        <v>1,262</v>
       </c>
       <c r="G83" t="str">
         <v>added Sept 2022</v>
       </c>
     </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>FDA (dev)</v>
+      </c>
+      <c r="D84" t="str">
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3040</v>
+      </c>
+      <c r="E84" t="str">
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3040</v>
+      </c>
+      <c r="F84" t="str">
+        <v>1,262</v>
+      </c>
+      <c r="G84" t="str">
+        <v>added Sept 2022</v>
+      </c>
+    </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>14)</v>
+        <v>15)</v>
       </c>
       <c r="B85" t="str">
-        <v>Labeling Section(s) [simple] "screen for" within HIGHLIGHTS</v>
+        <v>Chemical Structure (3)Tetralin [substructure] with NDA</v>
       </c>
       <c r="C85" t="str">
         <v xml:space="preserve">FDA   </v>
       </c>
       <c r="D85" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/117446</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/120940</v>
       </c>
       <c r="E85" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/117446</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/120940</v>
       </c>
       <c r="F85" t="str">
-        <v>1,257</v>
+        <v>255</v>
       </c>
       <c r="G85" t="str">
-        <v>added Sept 2022</v>
+        <v>added Sept 2022; changed structure Nov 2022</v>
       </c>
     </row>
     <row r="86">
@@ -1547,16 +1594,16 @@
         <v>FDA (test)</v>
       </c>
       <c r="D86" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1192</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1232</v>
       </c>
       <c r="E86" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1192</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1232</v>
       </c>
       <c r="F86" t="str">
-        <v>1,262</v>
+        <v>255</v>
       </c>
       <c r="G86" t="str">
-        <v>added Sept 2022</v>
+        <v>added Nov 2022</v>
       </c>
     </row>
     <row r="87">
@@ -1564,36 +1611,53 @@
         <v>FDA (dev)</v>
       </c>
       <c r="D87" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3040</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3119</v>
       </c>
       <c r="E87" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3040</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3119</v>
       </c>
       <c r="F87" t="str">
-        <v>1,262</v>
+        <v>255</v>
       </c>
       <c r="G87" t="str">
-        <v>added Sept 2022</v>
+        <v>added Nov 2022</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>Public</v>
+      </c>
+      <c r="D88" t="str">
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406947</v>
+      </c>
+      <c r="E88" t="str">
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406947</v>
+      </c>
+      <c r="F88" t="str">
+        <v>255</v>
+      </c>
+      <c r="G88" t="str">
+        <v>added Nov 2022; ERROR with query (see error notes)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>15)</v>
+        <v>16)</v>
       </c>
       <c r="B89" t="str">
-        <v>Chemical Structure (3)Tetralin [substructure] with NDA</v>
+        <v>Chemical Structure (3)Tetralin [substructure] without NDA</v>
       </c>
       <c r="C89" t="str">
         <v xml:space="preserve">FDA   </v>
       </c>
       <c r="D89" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/120940</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/120941</v>
       </c>
       <c r="E89" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/120940</v>
+        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/120941</v>
       </c>
       <c r="F89" t="str">
-        <v>255</v>
+        <v>2,770</v>
       </c>
       <c r="G89" t="str">
         <v>added Sept 2022; changed structure Nov 2022</v>
@@ -1604,16 +1668,16 @@
         <v>FDA (test)</v>
       </c>
       <c r="D90" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1232</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1233</v>
       </c>
       <c r="E90" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1232</v>
+        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1233</v>
       </c>
       <c r="F90" t="str">
-        <v>255</v>
+        <v>2,770</v>
       </c>
       <c r="G90" t="str">
-        <v>added Nov 2022</v>
+        <v>added Sept 2022; changed structure Nov 2022</v>
       </c>
     </row>
     <row r="91">
@@ -1621,13 +1685,13 @@
         <v>FDA (dev)</v>
       </c>
       <c r="D91" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3119</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3120</v>
       </c>
       <c r="E91" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3119</v>
+        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3120</v>
       </c>
       <c r="F91" t="str">
-        <v>255</v>
+        <v>2,770</v>
       </c>
       <c r="G91" t="str">
         <v>added Nov 2022</v>
@@ -1638,141 +1702,67 @@
         <v>Public</v>
       </c>
       <c r="D92" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406947</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406860</v>
       </c>
       <c r="E92" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406947</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406860</v>
       </c>
       <c r="F92" t="str">
-        <v>255</v>
+        <v>2,770</v>
       </c>
       <c r="G92" t="str">
-        <v>added Nov 2022; ERROR with query (see error notes)</v>
+        <v>added Nov 2022</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>16)</v>
+        <v>13)</v>
       </c>
       <c r="B93" t="str">
-        <v>Chemical Structure (3)Tetralin [substructure] without NDA</v>
+        <v>MedDRA Terms "acute liver failure" or PT or LLTs within WARNINGS AND PRECAUTIONS</v>
       </c>
       <c r="C93" t="str">
-        <v xml:space="preserve">FDA   </v>
+        <v>Public</v>
       </c>
       <c r="D93" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/search/spl-summaries/criteria/120941</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406656</v>
       </c>
       <c r="E93" t="str">
-        <v>http://fdalabel.fda.gov/fdalabel/ui/spl-summaries/criteria/120941</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406656</v>
       </c>
       <c r="F93" t="str">
-        <v>2,770</v>
+        <v>596</v>
       </c>
       <c r="G93" t="str">
-        <v>added Sept 2022; changed structure Nov 2022</v>
+        <v>waiting for production; updated Nov 2022</v>
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="str">
+        <v>14)</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Labeling Section(s) [simple] "screen for" within HIGHLIGHTS</v>
+      </c>
       <c r="C94" t="str">
-        <v>FDA (test)</v>
+        <v>Public</v>
       </c>
       <c r="D94" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/search/spl-summaries/criteria/1233</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406658</v>
       </c>
       <c r="E94" t="str">
-        <v>http://ncsvmlblapptst2.fda.gov/fdalabel/ui/spl-summaries/criteria/1233</v>
+        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406658</v>
       </c>
       <c r="F94" t="str">
-        <v>2,770</v>
+        <v>1,292</v>
       </c>
       <c r="G94" t="str">
-        <v>added Sept 2022; changed structure Nov 2022</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="C95" t="str">
-        <v>FDA (dev)</v>
-      </c>
-      <c r="D95" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/search/spl-summaries/criteria/3120</v>
-      </c>
-      <c r="E95" t="str">
-        <v>http://ncsvmdbbapp-dev.fda.gov:8080/fdalabel/ui/spl-summaries/criteria/3120</v>
-      </c>
-      <c r="F95" t="str">
-        <v>2,770</v>
-      </c>
-      <c r="G95" t="str">
-        <v>added Nov 2022</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="C96" t="str">
-        <v>Public</v>
-      </c>
-      <c r="D96" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406860</v>
-      </c>
-      <c r="E96" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406860</v>
-      </c>
-      <c r="F96" t="str">
-        <v>2,770</v>
-      </c>
-      <c r="G96" t="str">
-        <v>added Nov 2022</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>13)</v>
-      </c>
-      <c r="B97" t="str">
-        <v>MedDRA Terms "acute liver failure" or PT or LLTs within WARNINGS AND PRECAUTIONS</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Public</v>
-      </c>
-      <c r="D97" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406656</v>
-      </c>
-      <c r="E97" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406656</v>
-      </c>
-      <c r="F97" t="str">
-        <v>596</v>
-      </c>
-      <c r="G97" t="str">
-        <v>waiting for production; updated Nov 2022</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>14)</v>
-      </c>
-      <c r="B98" t="str">
-        <v>Labeling Section(s) [simple] "screen for" within HIGHLIGHTS</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Public</v>
-      </c>
-      <c r="D98" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/search/spl-summaries/criteria/406658</v>
-      </c>
-      <c r="E98" t="str">
-        <v>https://nctr-crs.fda.gov/fdalabel/ui/spl-summaries/criteria/406658</v>
-      </c>
-      <c r="F98" t="str">
-        <v>1,292</v>
-      </c>
-      <c r="G98" t="str">
         <v>waiting for production; updated Nov 2022</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G94"/>
   </ignoredErrors>
 </worksheet>
 </file>